--- a/Sensitivity_SSIM_Woman.xlsx
+++ b/Sensitivity_SSIM_Woman.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB8D16DC-6EBB-4312-9454-7494655BA5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EA1BBFC-1BDA-4350-9AB6-DA19230D2CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5FCAA1A5-14B7-47A9-AC14-F538CE575799}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{92B7757A-3D44-4455-8420-1686C1092A8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CC9754-D62B-4D2D-9F8E-CC3347EA2263}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C8677C-3AB4-4010-80A5-6FE4E88494BA}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{110CD293-6FC7-4BD4-8C21-59797252E5DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8368E027-BE0B-47F0-9FC4-1DB3BE133194}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{595B2E2F-6002-4CE6-A0C4-4966DAE4BB5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5EBF54A-642A-421F-A289-8B45DCDE048A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
